--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_10/epoch_10/per_file_predictions_epoch_10.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_10/epoch_10/per_file_predictions_epoch_10.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.7588,0.1419,0.1958,0.0158</t>
-  </si>
-  <si>
-    <t>0.5391,0.2508,0.3120,0.0228</t>
-  </si>
-  <si>
-    <t>0.6826,0.1716,0.2716,0.0154</t>
-  </si>
-  <si>
-    <t>0.7698,0.0837,0.2527,0.0178</t>
-  </si>
-  <si>
-    <t>0.6374,0.2194,0.2639,0.0271</t>
-  </si>
-  <si>
-    <t>0.5693,0.2838,0.2324,0.0105</t>
-  </si>
-  <si>
-    <t>0.5840,0.2818,0.2381,0.0121</t>
-  </si>
-  <si>
-    <t>0.7467,0.1174,0.2175,0.0168</t>
-  </si>
-  <si>
-    <t>0.6529,0.2720,0.2043,0.0168</t>
-  </si>
-  <si>
-    <t>0.7060,0.2096,0.2082,0.0128</t>
-  </si>
-  <si>
-    <t>0.6218,0.2857,0.1980,0.0140</t>
-  </si>
-  <si>
-    <t>0.7024,0.1869,0.2182,0.0159</t>
-  </si>
-  <si>
-    <t>0.7218,0.1681,0.2069,0.0162</t>
-  </si>
-  <si>
-    <t>0.6821,0.2114,0.2245,0.0167</t>
-  </si>
-  <si>
-    <t>0.4956,0.3797,0.2467,0.0111</t>
-  </si>
-  <si>
-    <t>0.4865,0.2094,0.4341,0.0250</t>
-  </si>
-  <si>
-    <t>0.6241,0.1759,0.3146,0.0220</t>
-  </si>
-  <si>
-    <t>0.4427,0.3730,0.3072,0.0132</t>
-  </si>
-  <si>
-    <t>0.4231,0.3740,0.2706,0.0078</t>
-  </si>
-  <si>
-    <t>0.4645,0.3583,0.2547,0.0110</t>
-  </si>
-  <si>
-    <t>0.5195,0.2962,0.2641,0.0082</t>
-  </si>
-  <si>
-    <t>0.3880,0.4424,0.2511,0.0090</t>
-  </si>
-  <si>
-    <t>0.6509,0.1224,0.3163,0.0517</t>
-  </si>
-  <si>
-    <t>0.5708,0.3161,0.2900,0.0224</t>
-  </si>
-  <si>
-    <t>0.6666,0.0343,0.4589,0.0165</t>
-  </si>
-  <si>
-    <t>0.6226,0.1462,0.3652,0.0252</t>
-  </si>
-  <si>
-    <t>0.5263,0.1945,0.4204,0.0228</t>
-  </si>
-  <si>
-    <t>0.6101,0.2343,0.3075,0.0396</t>
-  </si>
-  <si>
-    <t>0.6217,0.1163,0.4039,0.0129</t>
-  </si>
-  <si>
-    <t>0.6756,0.2026,0.2039,0.0084</t>
-  </si>
-  <si>
-    <t>0.5236,0.3713,0.2137,0.0100</t>
-  </si>
-  <si>
-    <t>0.1340,0.4879,0.6010,0.0242</t>
-  </si>
-  <si>
-    <t>0.5315,0.3421,0.2176,0.0110</t>
-  </si>
-  <si>
-    <t>0.6152,0.2799,0.2294,0.0196</t>
-  </si>
-  <si>
-    <t>0.3973,0.4043,0.3269,0.0180</t>
-  </si>
-  <si>
-    <t>0.6394,0.2801,0.1641,0.0072</t>
-  </si>
-  <si>
-    <t>0.7098,0.1918,0.2151,0.0156</t>
-  </si>
-  <si>
-    <t>0.0747,0.8451,0.2172,0.0129</t>
-  </si>
-  <si>
-    <t>0.5240,0.3019,0.3259,0.0245</t>
-  </si>
-  <si>
-    <t>0.4041,0.2659,0.4535,0.0552</t>
-  </si>
-  <si>
-    <t>0.5798,0.0829,0.4543,0.0480</t>
-  </si>
-  <si>
-    <t>0.3079,0.3447,0.5216,0.0315</t>
-  </si>
-  <si>
-    <t>0.0742,0.8508,0.2166,0.0085</t>
-  </si>
-  <si>
-    <t>0.2808,0.3371,0.5624,0.0228</t>
-  </si>
-  <si>
-    <t>0.3590,0.3873,0.4078,0.0255</t>
-  </si>
-  <si>
-    <t>0.4051,0.4336,0.2229,0.0083</t>
-  </si>
-  <si>
-    <t>0.3728,0.5666,0.2066,0.0125</t>
-  </si>
-  <si>
-    <t>0.2567,0.6364,0.2073,0.0065</t>
-  </si>
-  <si>
-    <t>0.0440,0.5501,0.7796,0.0273</t>
-  </si>
-  <si>
-    <t>0.4209,0.2511,0.4800,0.0305</t>
-  </si>
-  <si>
-    <t>0.6248,0.1756,0.3220,0.0168</t>
-  </si>
-  <si>
-    <t>0.7210,0.0715,0.3465,0.0214</t>
-  </si>
-  <si>
-    <t>0.3271,0.1277,0.6574,0.0200</t>
-  </si>
-  <si>
-    <t>0.5326,0.1890,0.4245,0.0134</t>
-  </si>
-  <si>
-    <t>0.7028,0.1746,0.2381,0.0129</t>
-  </si>
-  <si>
-    <t>0.6905,0.1604,0.2369,0.0081</t>
-  </si>
-  <si>
-    <t>0.3588,0.4291,0.3467,0.0198</t>
-  </si>
-  <si>
-    <t>0.1852,0.3078,0.6969,0.0314</t>
-  </si>
-  <si>
-    <t>0.5821,0.2187,0.3368,0.0309</t>
-  </si>
-  <si>
-    <t>0.7078,0.1885,0.2310,0.0192</t>
-  </si>
-  <si>
-    <t>0.7231,0.2080,0.1743,0.0103</t>
-  </si>
-  <si>
-    <t>0.0664,0.7615,0.5033,0.0171</t>
-  </si>
-  <si>
-    <t>0.0244,0.6113,0.8432,0.0128</t>
-  </si>
-  <si>
-    <t>0.4746,0.1216,0.4953,0.0579</t>
-  </si>
-  <si>
-    <t>0.0266,0.9210,0.3712,0.0037</t>
-  </si>
-  <si>
-    <t>0.1247,0.4781,0.6666,0.0354</t>
-  </si>
-  <si>
-    <t>0.5864,0.4136,0.1203,0.0043</t>
-  </si>
-  <si>
-    <t>0.1165,0.9240,0.0194,0.0007</t>
-  </si>
-  <si>
-    <t>0.8746,0.0961,0.1070,0.0076</t>
-  </si>
-  <si>
-    <t>0.6601,0.2246,0.1859,0.0069</t>
-  </si>
-  <si>
-    <t>0.0835,0.6269,0.6171,0.0167</t>
-  </si>
-  <si>
-    <t>0.1684,0.5494,0.4885,0.0151</t>
-  </si>
-  <si>
-    <t>0.1350,0.6041,0.5224,0.0296</t>
-  </si>
-  <si>
-    <t>0.0550,0.9167,0.1154,0.0026</t>
-  </si>
-  <si>
-    <t>0.0720,0.9102,0.0898,0.0021</t>
-  </si>
-  <si>
-    <t>0.6993,0.0885,0.3205,0.0390</t>
-  </si>
-  <si>
-    <t>0.5831,0.1203,0.3828,0.0450</t>
-  </si>
-  <si>
-    <t>0.7744,0.0739,0.2541,0.0212</t>
-  </si>
-  <si>
-    <t>0.6880,0.1440,0.2590,0.0231</t>
-  </si>
-  <si>
-    <t>0.6860,0.0721,0.3011,0.0423</t>
-  </si>
-  <si>
-    <t>0.6861,0.1191,0.3009,0.0240</t>
-  </si>
-  <si>
-    <t>0.0597,0.8360,0.4698,0.0121</t>
-  </si>
-  <si>
-    <t>0.0833,0.7633,0.4208,0.0084</t>
-  </si>
-  <si>
-    <t>0.1442,0.5546,0.5871,0.0179</t>
-  </si>
-  <si>
-    <t>0.1564,0.5709,0.5218,0.0277</t>
-  </si>
-  <si>
-    <t>0.0463,0.8787,0.3637,0.0046</t>
-  </si>
-  <si>
-    <t>0.2948,0.4171,0.5314,0.0572</t>
-  </si>
-  <si>
-    <t>0.6509,0.2543,0.1761,0.0111</t>
-  </si>
-  <si>
-    <t>0.7431,0.2035,0.1603,0.0135</t>
-  </si>
-  <si>
-    <t>0.5796,0.2379,0.2976,0.0150</t>
-  </si>
-  <si>
-    <t>0.6267,0.2470,0.2359,0.0179</t>
-  </si>
-  <si>
-    <t>0.6426,0.2514,0.2037,0.0109</t>
-  </si>
-  <si>
-    <t>0.6454,0.2291,0.2244,0.0172</t>
-  </si>
-  <si>
-    <t>0.5113,0.3044,0.2743,0.0151</t>
-  </si>
-  <si>
-    <t>0.7080,0.2197,0.1563,0.0098</t>
-  </si>
-  <si>
-    <t>0.6947,0.1971,0.2304,0.0221</t>
-  </si>
-  <si>
-    <t>0.4181,0.4250,0.2798,0.0243</t>
-  </si>
-  <si>
-    <t>0.6668,0.1818,0.2555,0.0344</t>
-  </si>
-  <si>
-    <t>0.8454,0.1536,0.0950,0.0109</t>
-  </si>
-  <si>
-    <t>0.6851,0.2648,0.1846,0.0192</t>
-  </si>
-  <si>
-    <t>0.6918,0.2017,0.2370,0.0157</t>
-  </si>
-  <si>
-    <t>0.5898,0.3167,0.2239,0.0199</t>
-  </si>
-  <si>
-    <t>0.5863,0.2601,0.2556,0.0182</t>
-  </si>
-  <si>
-    <t>0.0804,0.2972,0.7995,0.0269</t>
-  </si>
-  <si>
-    <t>0.5909,0.2267,0.3537,0.0263</t>
-  </si>
-  <si>
-    <t>0.5643,0.1115,0.4411,0.0264</t>
-  </si>
-  <si>
-    <t>0.6700,0.1155,0.3195,0.0280</t>
-  </si>
-  <si>
-    <t>0.2491,0.6229,0.2359,0.0094</t>
-  </si>
-  <si>
-    <t>0.4423,0.3038,0.2900,0.0093</t>
-  </si>
-  <si>
-    <t>0.2296,0.6014,0.2947,0.0112</t>
-  </si>
-  <si>
-    <t>0.2893,0.5476,0.3203,0.0145</t>
-  </si>
-  <si>
-    <t>0.3999,0.4856,0.2341,0.0116</t>
-  </si>
-  <si>
-    <t>0.1591,0.7419,0.2083,0.0043</t>
-  </si>
-  <si>
-    <t>0.6608,0.1675,0.2253,0.0092</t>
-  </si>
-  <si>
-    <t>0.6095,0.1811,0.3347,0.0244</t>
-  </si>
-  <si>
-    <t>0.5295,0.2584,0.3762,0.0243</t>
-  </si>
-  <si>
-    <t>0.5505,0.2676,0.3299,0.0267</t>
-  </si>
-  <si>
-    <t>0.4903,0.3027,0.3086,0.0224</t>
-  </si>
-  <si>
-    <t>0.5322,0.2578,0.3658,0.0387</t>
-  </si>
-  <si>
-    <t>0.2596,0.6155,0.1889,0.0042</t>
-  </si>
-  <si>
-    <t>0.1612,0.7923,0.1694,0.0058</t>
-  </si>
-  <si>
-    <t>0.3110,0.5137,0.3036,0.0134</t>
-  </si>
-  <si>
-    <t>0.1445,0.7557,0.2267,0.0055</t>
-  </si>
-  <si>
-    <t>0.6848,0.2538,0.1503,0.0067</t>
-  </si>
-  <si>
-    <t>0.5539,0.3267,0.1926,0.0087</t>
-  </si>
-  <si>
-    <t>0.4671,0.3703,0.2366,0.0083</t>
-  </si>
-  <si>
-    <t>0.6011,0.2630,0.2343,0.0149</t>
-  </si>
-  <si>
-    <t>0.4873,0.2737,0.3504,0.0229</t>
-  </si>
-  <si>
-    <t>0.5909,0.3120,0.2333,0.0215</t>
-  </si>
-  <si>
-    <t>0.7828,0.1360,0.1562,0.0093</t>
-  </si>
-  <si>
-    <t>0.7235,0.1372,0.2239,0.0144</t>
-  </si>
-  <si>
-    <t>0.7152,0.1950,0.1910,0.0102</t>
-  </si>
-  <si>
-    <t>0.6524,0.2120,0.2272,0.0122</t>
-  </si>
-  <si>
-    <t>0.7760,0.1201,0.1870,0.0121</t>
-  </si>
-  <si>
-    <t>0.3075,0.4176,0.3981,0.0115</t>
-  </si>
-  <si>
-    <t>0.1918,0.5456,0.5175,0.0349</t>
-  </si>
-  <si>
-    <t>0.2115,0.7314,0.1569,0.0048</t>
-  </si>
-  <si>
-    <t>0.3092,0.3106,0.5386,0.0225</t>
-  </si>
-  <si>
-    <t>0.5665,0.2249,0.3122,0.0143</t>
-  </si>
-  <si>
-    <t>0.6957,0.1183,0.2989,0.0209</t>
-  </si>
-  <si>
-    <t>0.7292,0.1935,0.2016,0.0181</t>
-  </si>
-  <si>
-    <t>0.7142,0.1995,0.2345,0.0170</t>
-  </si>
-  <si>
-    <t>0.8143,0.0484,0.2408,0.0187</t>
-  </si>
-  <si>
-    <t>0.5624,0.0951,0.3925,0.0654</t>
-  </si>
-  <si>
-    <t>0.7482,0.1133,0.2226,0.0219</t>
-  </si>
-  <si>
-    <t>0.7624,0.0886,0.2482,0.0286</t>
-  </si>
-  <si>
-    <t>0.0585,0.7385,0.5216,0.0150</t>
-  </si>
-  <si>
-    <t>0.7155,0.1807,0.2193,0.0121</t>
-  </si>
-  <si>
-    <t>0.4175,0.3546,0.3258,0.0189</t>
-  </si>
-  <si>
-    <t>0.6323,0.1897,0.3032,0.0264</t>
-  </si>
-  <si>
-    <t>0.6253,0.2194,0.2302,0.0133</t>
-  </si>
-  <si>
-    <t>0.6260,0.1300,0.3639,0.0251</t>
-  </si>
-  <si>
-    <t>0.7858,0.1513,0.1511,0.0153</t>
-  </si>
-  <si>
-    <t>0.6583,0.1899,0.2486,0.0166</t>
-  </si>
-  <si>
-    <t>0.0775,0.4084,0.7913,0.0502</t>
-  </si>
-  <si>
-    <t>0.7818,0.1197,0.1729,0.0167</t>
-  </si>
-  <si>
-    <t>0.6506,0.2215,0.2602,0.0366</t>
-  </si>
-  <si>
-    <t>0.6794,0.2446,0.1647,0.0097</t>
-  </si>
-  <si>
-    <t>0.8242,0.0644,0.2075,0.0100</t>
-  </si>
-  <si>
-    <t>0.6310,0.1957,0.2825,0.0241</t>
-  </si>
-  <si>
-    <t>0.5085,0.3029,0.3082,0.0201</t>
-  </si>
-  <si>
-    <t>0.6996,0.1817,0.2380,0.0139</t>
-  </si>
-  <si>
-    <t>0.7640,0.1513,0.1759,0.0141</t>
-  </si>
-  <si>
-    <t>0.7371,0.1390,0.2210,0.0186</t>
-  </si>
-  <si>
-    <t>0.4921,0.3739,0.2750,0.0244</t>
-  </si>
-  <si>
-    <t>0.5772,0.2246,0.2619,0.0159</t>
-  </si>
-  <si>
-    <t>0.7680,0.1309,0.1987,0.0137</t>
-  </si>
-  <si>
-    <t>0.5853,0.2413,0.2884,0.0202</t>
-  </si>
-  <si>
-    <t>0.6133,0.3225,0.1727,0.0133</t>
-  </si>
-  <si>
-    <t>0.7761,0.1546,0.1580,0.0116</t>
-  </si>
-  <si>
-    <t>0.6684,0.1752,0.2483,0.0208</t>
-  </si>
-  <si>
-    <t>0.3364,0.5169,0.2674,0.0108</t>
-  </si>
-  <si>
-    <t>0.4092,0.4071,0.2753,0.0110</t>
-  </si>
-  <si>
-    <t>0.3295,0.4997,0.2936,0.0131</t>
-  </si>
-  <si>
-    <t>0.6237,0.3044,0.2587,0.0295</t>
-  </si>
-  <si>
-    <t>0.3482,0.4715,0.3004,0.0162</t>
-  </si>
-  <si>
-    <t>0.6635,0.2455,0.2096,0.0148</t>
-  </si>
-  <si>
-    <t>0.6500,0.2547,0.2066,0.0137</t>
-  </si>
-  <si>
-    <t>0.6746,0.2250,0.2022,0.0158</t>
-  </si>
-  <si>
-    <t>0.2010,0.5130,0.4797,0.0179</t>
-  </si>
-  <si>
-    <t>0.8453,0.0784,0.1543,0.0099</t>
-  </si>
-  <si>
-    <t>0.2096,0.4624,0.4680,0.0306</t>
-  </si>
-  <si>
-    <t>0.2147,0.4211,0.5814,0.0321</t>
-  </si>
-  <si>
-    <t>0.6503,0.1062,0.3497,0.0124</t>
-  </si>
-  <si>
-    <t>0.0388,0.4954,0.8682,0.0133</t>
-  </si>
-  <si>
-    <t>0.4797,0.2253,0.4464,0.0194</t>
-  </si>
-  <si>
-    <t>0.5348,0.2055,0.3563,0.0120</t>
-  </si>
-  <si>
-    <t>0.6457,0.1272,0.3566,0.0207</t>
-  </si>
-  <si>
-    <t>0.6390,0.1591,0.3279,0.0259</t>
-  </si>
-  <si>
-    <t>0.4760,0.1430,0.5063,0.0226</t>
-  </si>
-  <si>
-    <t>0.6799,0.1511,0.2447,0.0090</t>
-  </si>
-  <si>
-    <t>0.7394,0.1697,0.2053,0.0121</t>
-  </si>
-  <si>
-    <t>0.6135,0.2876,0.2288,0.0123</t>
-  </si>
-  <si>
-    <t>0.4760,0.3349,0.3033,0.0171</t>
-  </si>
-  <si>
-    <t>0.5565,0.3007,0.2832,0.0232</t>
-  </si>
-  <si>
-    <t>0.4739,0.4196,0.2748,0.0187</t>
-  </si>
-  <si>
-    <t>0.4041,0.4642,0.2513,0.0166</t>
-  </si>
-  <si>
-    <t>0.5842,0.2836,0.2331,0.0140</t>
-  </si>
-  <si>
-    <t>0.4294,0.3933,0.2929,0.0132</t>
-  </si>
-  <si>
-    <t>0.6198,0.1926,0.3166,0.0291</t>
-  </si>
-  <si>
-    <t>0.6586,0.2655,0.2001,0.0138</t>
-  </si>
-  <si>
-    <t>0.7499,0.1471,0.1883,0.0082</t>
-  </si>
-  <si>
-    <t>0.7219,0.1376,0.2498,0.0144</t>
-  </si>
-  <si>
-    <t>0.5751,0.1378,0.4084,0.0481</t>
-  </si>
-  <si>
-    <t>0.7069,0.1292,0.2757,0.0203</t>
-  </si>
-  <si>
-    <t>0.6080,0.1254,0.3699,0.0238</t>
-  </si>
-  <si>
-    <t>0.6674,0.1490,0.3095,0.0258</t>
-  </si>
-  <si>
-    <t>0.3028,0.4563,0.4655,0.0445</t>
-  </si>
-  <si>
-    <t>0.2720,0.4328,0.5084,0.0351</t>
-  </si>
-  <si>
-    <t>0.4735,0.1368,0.5268,0.0383</t>
-  </si>
-  <si>
-    <t>0.1333,0.6185,0.5441,0.0297</t>
-  </si>
-  <si>
-    <t>0.6853,0.1624,0.2672,0.0248</t>
-  </si>
-  <si>
-    <t>0.5458,0.2852,0.3139,0.0301</t>
-  </si>
-  <si>
-    <t>0.5488,0.2839,0.2599,0.0181</t>
-  </si>
-  <si>
-    <t>0.7260,0.1833,0.1821,0.0125</t>
-  </si>
-  <si>
-    <t>0.6903,0.2962,0.1534,0.0075</t>
-  </si>
-  <si>
-    <t>0.6079,0.2673,0.2584,0.0225</t>
-  </si>
-  <si>
-    <t>0.5830,0.2935,0.2363,0.0169</t>
-  </si>
-  <si>
-    <t>0.6177,0.2509,0.2195,0.0131</t>
-  </si>
-  <si>
-    <t>0.4378,0.3436,0.3395,0.0227</t>
-  </si>
-  <si>
-    <t>0.6602,0.1912,0.2471,0.0144</t>
-  </si>
-  <si>
-    <t>0.6761,0.1412,0.2853,0.0175</t>
-  </si>
-  <si>
-    <t>0.2732,0.3040,0.5544,0.0248</t>
-  </si>
-  <si>
-    <t>0.2951,0.3924,0.4211,0.0120</t>
-  </si>
-  <si>
-    <t>0.3524,0.5858,0.1455,0.0059</t>
-  </si>
-  <si>
-    <t>0.2849,0.2316,0.6108,0.0137</t>
-  </si>
-  <si>
-    <t>0.5551,0.2626,0.3748,0.0290</t>
-  </si>
-  <si>
-    <t>0.0206,0.3820,0.9121,0.0097</t>
-  </si>
-  <si>
-    <t>0.6097,0.1230,0.3919,0.0148</t>
-  </si>
-  <si>
-    <t>0.4868,0.3277,0.3239,0.0238</t>
-  </si>
-  <si>
-    <t>0.5921,0.1760,0.3610,0.0423</t>
-  </si>
-  <si>
-    <t>0.6274,0.1965,0.2992,0.0322</t>
-  </si>
-  <si>
-    <t>0.5925,0.2201,0.3315,0.0284</t>
-  </si>
-  <si>
-    <t>0.6195,0.2689,0.2606,0.0286</t>
-  </si>
-  <si>
-    <t>0.5955,0.2740,0.2427,0.0127</t>
-  </si>
-  <si>
-    <t>0.6989,0.2160,0.1901,0.0139</t>
-  </si>
-  <si>
-    <t>0.7303,0.1583,0.2005,0.0154</t>
-  </si>
-  <si>
-    <t>0.6013,0.2793,0.2510,0.0247</t>
-  </si>
-  <si>
-    <t>0.6134,0.2187,0.2670,0.0177</t>
-  </si>
-  <si>
-    <t>0.5444,0.3466,0.2353,0.0223</t>
-  </si>
-  <si>
-    <t>0.7706,0.1614,0.1615,0.0101</t>
-  </si>
-  <si>
-    <t>0.4671,0.3228,0.3394,0.0109</t>
-  </si>
-  <si>
-    <t>0.1527,0.2813,0.7342,0.0247</t>
-  </si>
-  <si>
-    <t>0.2855,0.3804,0.4456,0.0249</t>
-  </si>
-  <si>
-    <t>0.4733,0.3513,0.3327,0.0184</t>
-  </si>
-  <si>
-    <t>0.4838,0.1211,0.5507,0.0331</t>
-  </si>
-  <si>
-    <t>0.6296,0.0942,0.3932,0.0316</t>
-  </si>
-  <si>
-    <t>0.6100,0.1283,0.3985,0.0209</t>
-  </si>
-  <si>
-    <t>0.2059,0.3201,0.6175,0.1153</t>
-  </si>
-  <si>
-    <t>0.6586,0.2009,0.2245,0.0162</t>
-  </si>
-  <si>
-    <t>0.6531,0.1117,0.3379,0.0387</t>
-  </si>
-  <si>
-    <t>0.6676,0.1199,0.3146,0.0231</t>
-  </si>
-  <si>
-    <t>0.8194,0.0305,0.2470,0.0131</t>
-  </si>
-  <si>
-    <t>0.7069,0.0868,0.3052,0.0297</t>
-  </si>
-  <si>
-    <t>0.4648,0.2959,0.3376,0.0300</t>
+    <t>0.1374,0.0244,0.0051,0.9054</t>
+  </si>
+  <si>
+    <t>0.0235,0.0035,0.0009,0.9878</t>
+  </si>
+  <si>
+    <t>0.0696,0.0044,0.0015,0.9671</t>
+  </si>
+  <si>
+    <t>0.2761,0.0079,0.0057,0.8340</t>
+  </si>
+  <si>
+    <t>0.9968,0.0017,0.0004,0.0018</t>
+  </si>
+  <si>
+    <t>0.9953,0.0010,0.0003,0.0041</t>
+  </si>
+  <si>
+    <t>0.9950,0.0029,0.0010,0.0025</t>
+  </si>
+  <si>
+    <t>0.9927,0.0008,0.0003,0.0083</t>
+  </si>
+  <si>
+    <t>0.9930,0.0021,0.0007,0.0058</t>
+  </si>
+  <si>
+    <t>0.9951,0.0022,0.0005,0.0034</t>
+  </si>
+  <si>
+    <t>0.9967,0.0022,0.0006,0.0014</t>
+  </si>
+  <si>
+    <t>0.9954,0.0022,0.0006,0.0027</t>
+  </si>
+  <si>
+    <t>0.5522,0.2495,0.2767,0.0846</t>
+  </si>
+  <si>
+    <t>0.1408,0.0295,0.8546,0.0199</t>
+  </si>
+  <si>
+    <t>0.6689,0.0281,0.4551,0.0079</t>
+  </si>
+  <si>
+    <t>0.0800,0.0246,0.9148,0.0077</t>
+  </si>
+  <si>
+    <t>0.5589,0.1055,0.2424,0.2264</t>
+  </si>
+  <si>
+    <t>0.1556,0.8881,0.0217,0.0096</t>
+  </si>
+  <si>
+    <t>0.1752,0.8352,0.0700,0.0120</t>
+  </si>
+  <si>
+    <t>0.7682,0.3412,0.0354,0.0142</t>
+  </si>
+  <si>
+    <t>0.3056,0.7121,0.0650,0.0088</t>
+  </si>
+  <si>
+    <t>0.2124,0.7869,0.0754,0.0150</t>
+  </si>
+  <si>
+    <t>0.5821,0.0301,0.4737,0.0599</t>
+  </si>
+  <si>
+    <t>0.2153,0.0343,0.7696,0.0442</t>
+  </si>
+  <si>
+    <t>0.2429,0.0741,0.7160,0.0698</t>
+  </si>
+  <si>
+    <t>0.3307,0.0632,0.6932,0.0428</t>
+  </si>
+  <si>
+    <t>0.3385,0.0341,0.7308,0.0198</t>
+  </si>
+  <si>
+    <t>0.4804,0.0174,0.6329,0.0221</t>
+  </si>
+  <si>
+    <t>0.0267,0.0134,0.9605,0.0115</t>
+  </si>
+  <si>
+    <t>0.6941,0.3413,0.0830,0.0236</t>
+  </si>
+  <si>
+    <t>0.4444,0.1402,0.4791,0.1185</t>
+  </si>
+  <si>
+    <t>0.0110,0.0927,0.9259,0.0322</t>
+  </si>
+  <si>
+    <t>0.0609,0.8186,0.3041,0.0200</t>
+  </si>
+  <si>
+    <t>0.6073,0.1567,0.2114,0.1688</t>
+  </si>
+  <si>
+    <t>0.7168,0.1060,0.2008,0.0636</t>
+  </si>
+  <si>
+    <t>0.9100,0.0758,0.0375,0.0097</t>
+  </si>
+  <si>
+    <t>0.1220,0.7533,0.3096,0.0143</t>
+  </si>
+  <si>
+    <t>0.0224,0.9229,0.0798,0.0160</t>
+  </si>
+  <si>
+    <t>0.1979,0.2072,0.6637,0.0497</t>
+  </si>
+  <si>
+    <t>0.1676,0.1498,0.7219,0.0179</t>
+  </si>
+  <si>
+    <t>0.2243,0.0351,0.5525,0.2524</t>
+  </si>
+  <si>
+    <t>0.0641,0.1173,0.8856,0.0230</t>
+  </si>
+  <si>
+    <t>0.0245,0.9534,0.0259,0.0035</t>
+  </si>
+  <si>
+    <t>0.0872,0.4922,0.5714,0.0194</t>
+  </si>
+  <si>
+    <t>0.0691,0.1114,0.0586,0.8938</t>
+  </si>
+  <si>
+    <t>0.0082,0.9839,0.0078,0.0068</t>
+  </si>
+  <si>
+    <t>0.0214,0.9602,0.0286,0.0076</t>
+  </si>
+  <si>
+    <t>0.0028,0.9920,0.0072,0.0020</t>
+  </si>
+  <si>
+    <t>0.0697,0.4336,0.6682,0.0382</t>
+  </si>
+  <si>
+    <t>0.0141,0.2547,0.9387,0.0079</t>
+  </si>
+  <si>
+    <t>0.1607,0.0422,0.8209,0.0337</t>
+  </si>
+  <si>
+    <t>0.0575,0.0057,0.9406,0.0104</t>
+  </si>
+  <si>
+    <t>0.0653,0.1982,0.8295,0.0631</t>
+  </si>
+  <si>
+    <t>0.0552,0.0469,0.9279,0.0071</t>
+  </si>
+  <si>
+    <t>0.9897,0.0100,0.0023,0.0027</t>
+  </si>
+  <si>
+    <t>0.9844,0.0036,0.0012,0.0139</t>
+  </si>
+  <si>
+    <t>0.9848,0.0085,0.0015,0.0073</t>
+  </si>
+  <si>
+    <t>0.1095,0.2739,0.7300,0.0832</t>
+  </si>
+  <si>
+    <t>0.9949,0.0034,0.0012,0.0021</t>
+  </si>
+  <si>
+    <t>0.9964,0.0033,0.0007,0.0011</t>
+  </si>
+  <si>
+    <t>0.9877,0.0106,0.0026,0.0036</t>
+  </si>
+  <si>
+    <t>0.0112,0.8099,0.7250,0.0056</t>
+  </si>
+  <si>
+    <t>0.0072,0.3393,0.9513,0.0043</t>
+  </si>
+  <si>
+    <t>0.0155,0.0576,0.9522,0.0144</t>
+  </si>
+  <si>
+    <t>0.0083,0.7674,0.7734,0.0029</t>
+  </si>
+  <si>
+    <t>0.0157,0.1593,0.9369,0.0100</t>
+  </si>
+  <si>
+    <t>0.0686,0.8182,0.3103,0.0175</t>
+  </si>
+  <si>
+    <t>0.0078,0.9932,0.0012,0.0003</t>
+  </si>
+  <si>
+    <t>0.8019,0.0442,0.1814,0.0490</t>
+  </si>
+  <si>
+    <t>0.6444,0.1916,0.2220,0.0770</t>
+  </si>
+  <si>
+    <t>0.0124,0.1811,0.8884,0.0266</t>
+  </si>
+  <si>
+    <t>0.0162,0.7356,0.6287,0.0103</t>
+  </si>
+  <si>
+    <t>0.0237,0.7416,0.6414,0.0092</t>
+  </si>
+  <si>
+    <t>0.0083,0.9857,0.0055,0.0011</t>
+  </si>
+  <si>
+    <t>0.0109,0.9538,0.1181,0.0045</t>
+  </si>
+  <si>
+    <t>0.0063,0.0019,0.0025,0.9943</t>
+  </si>
+  <si>
+    <t>0.0070,0.0021,0.0006,0.9958</t>
+  </si>
+  <si>
+    <t>0.0035,0.0011,0.0005,0.9977</t>
+  </si>
+  <si>
+    <t>0.0328,0.0041,0.0025,0.9813</t>
+  </si>
+  <si>
+    <t>0.0051,0.0011,0.0011,0.9960</t>
+  </si>
+  <si>
+    <t>0.0042,0.0032,0.0006,0.9969</t>
+  </si>
+  <si>
+    <t>0.0095,0.9419,0.2644,0.0044</t>
+  </si>
+  <si>
+    <t>0.0072,0.7842,0.8367,0.0028</t>
+  </si>
+  <si>
+    <t>0.0230,0.8812,0.3898,0.0090</t>
+  </si>
+  <si>
+    <t>0.0348,0.3668,0.8232,0.0154</t>
+  </si>
+  <si>
+    <t>0.0210,0.9351,0.1207,0.0028</t>
+  </si>
+  <si>
+    <t>0.0156,0.8725,0.4130,0.0106</t>
+  </si>
+  <si>
+    <t>0.9970,0.0013,0.0003,0.0019</t>
+  </si>
+  <si>
+    <t>0.9964,0.0027,0.0007,0.0014</t>
+  </si>
+  <si>
+    <t>0.9935,0.0036,0.0009,0.0035</t>
+  </si>
+  <si>
+    <t>0.9919,0.0062,0.0011,0.0036</t>
+  </si>
+  <si>
+    <t>0.9949,0.0020,0.0005,0.0033</t>
+  </si>
+  <si>
+    <t>0.9963,0.0020,0.0006,0.0017</t>
+  </si>
+  <si>
+    <t>0.9928,0.0025,0.0007,0.0045</t>
+  </si>
+  <si>
+    <t>0.9927,0.0073,0.0014,0.0019</t>
+  </si>
+  <si>
+    <t>0.9966,0.0014,0.0003,0.0021</t>
+  </si>
+  <si>
+    <t>0.9969,0.0022,0.0005,0.0014</t>
+  </si>
+  <si>
+    <t>0.9942,0.0023,0.0009,0.0042</t>
+  </si>
+  <si>
+    <t>0.9942,0.0027,0.0007,0.0034</t>
+  </si>
+  <si>
+    <t>0.9949,0.0012,0.0004,0.0045</t>
+  </si>
+  <si>
+    <t>0.9951,0.0038,0.0012,0.0027</t>
+  </si>
+  <si>
+    <t>0.9951,0.0016,0.0004,0.0037</t>
+  </si>
+  <si>
+    <t>0.9978,0.0013,0.0004,0.0010</t>
+  </si>
+  <si>
+    <t>0.0030,0.0054,0.9813,0.0168</t>
+  </si>
+  <si>
+    <t>0.1305,0.0373,0.8624,0.0142</t>
+  </si>
+  <si>
+    <t>0.3830,0.4413,0.2005,0.3097</t>
+  </si>
+  <si>
+    <t>0.2127,0.0306,0.8075,0.0193</t>
+  </si>
+  <si>
+    <t>0.2129,0.8389,0.0247,0.0169</t>
+  </si>
+  <si>
+    <t>0.1676,0.8563,0.0363,0.0236</t>
+  </si>
+  <si>
+    <t>0.5626,0.5892,0.0142,0.0141</t>
+  </si>
+  <si>
+    <t>0.8159,0.2392,0.0432,0.0089</t>
+  </si>
+  <si>
+    <t>0.0964,0.8942,0.0555,0.0189</t>
+  </si>
+  <si>
+    <t>0.0463,0.9452,0.0304,0.0114</t>
+  </si>
+  <si>
+    <t>0.8757,0.1679,0.0302,0.0074</t>
+  </si>
+  <si>
+    <t>0.4304,0.3868,0.2579,0.1209</t>
+  </si>
+  <si>
+    <t>0.2762,0.0307,0.7694,0.0174</t>
+  </si>
+  <si>
+    <t>0.4107,0.4119,0.2162,0.2397</t>
+  </si>
+  <si>
+    <t>0.5018,0.1116,0.4555,0.1079</t>
+  </si>
+  <si>
+    <t>0.4380,0.1216,0.2063,0.3940</t>
+  </si>
+  <si>
+    <t>0.0048,0.9915,0.0087,0.0011</t>
+  </si>
+  <si>
+    <t>0.0075,0.9831,0.0147,0.0047</t>
+  </si>
+  <si>
+    <t>0.0257,0.9599,0.0244,0.0165</t>
+  </si>
+  <si>
+    <t>0.0024,0.9951,0.0036,0.0004</t>
+  </si>
+  <si>
+    <t>0.1067,0.7954,0.2738,0.0047</t>
+  </si>
+  <si>
+    <t>0.7790,0.2635,0.0579,0.0103</t>
+  </si>
+  <si>
+    <t>0.8898,0.1169,0.0384,0.0074</t>
+  </si>
+  <si>
+    <t>0.9916,0.0060,0.0023,0.0033</t>
+  </si>
+  <si>
+    <t>0.9928,0.0026,0.0008,0.0049</t>
+  </si>
+  <si>
+    <t>0.9376,0.0011,0.0005,0.1056</t>
+  </si>
+  <si>
+    <t>0.9718,0.0077,0.0037,0.0209</t>
+  </si>
+  <si>
+    <t>0.9922,0.0022,0.0009,0.0054</t>
+  </si>
+  <si>
+    <t>0.9926,0.0037,0.0016,0.0041</t>
+  </si>
+  <si>
+    <t>0.9856,0.0035,0.0014,0.0119</t>
+  </si>
+  <si>
+    <t>0.9826,0.0052,0.0022,0.0124</t>
+  </si>
+  <si>
+    <t>0.0190,0.7053,0.6945,0.0094</t>
+  </si>
+  <si>
+    <t>0.0160,0.8866,0.4177,0.0053</t>
+  </si>
+  <si>
+    <t>0.0359,0.5238,0.7554,0.0176</t>
+  </si>
+  <si>
+    <t>0.0563,0.6367,0.6217,0.0155</t>
+  </si>
+  <si>
+    <t>0.4996,0.3262,0.0382,0.2240</t>
+  </si>
+  <si>
+    <t>0.4486,0.1233,0.1923,0.3987</t>
+  </si>
+  <si>
+    <t>0.7571,0.0256,0.3398,0.0196</t>
+  </si>
+  <si>
+    <t>0.6642,0.0695,0.1796,0.1285</t>
+  </si>
+  <si>
+    <t>0.0081,0.0018,0.0035,0.9926</t>
+  </si>
+  <si>
+    <t>0.0006,0.0009,0.0003,0.9994</t>
+  </si>
+  <si>
+    <t>0.0061,0.0034,0.0009,0.9954</t>
+  </si>
+  <si>
+    <t>0.0236,0.0013,0.0016,0.9869</t>
+  </si>
+  <si>
+    <t>0.0057,0.9359,0.1633,0.0097</t>
+  </si>
+  <si>
+    <t>0.9797,0.0048,0.0015,0.0161</t>
+  </si>
+  <si>
+    <t>0.3272,0.7437,0.0323,0.0411</t>
+  </si>
+  <si>
+    <t>0.9890,0.0038,0.0011,0.0080</t>
+  </si>
+  <si>
+    <t>0.9188,0.1038,0.0151,0.0115</t>
+  </si>
+  <si>
+    <t>0.9265,0.0044,0.0017,0.0818</t>
+  </si>
+  <si>
+    <t>0.1365,0.0088,0.0110,0.9118</t>
+  </si>
+  <si>
+    <t>0.9298,0.0048,0.0025,0.0829</t>
+  </si>
+  <si>
+    <t>0.0097,0.0312,0.8799,0.1326</t>
+  </si>
+  <si>
+    <t>0.7301,0.0026,0.0015,0.4144</t>
+  </si>
+  <si>
+    <t>0.8501,0.0074,0.0059,0.1668</t>
+  </si>
+  <si>
+    <t>0.6470,0.2718,0.1084,0.1005</t>
+  </si>
+  <si>
+    <t>0.7828,0.1544,0.0278,0.0888</t>
+  </si>
+  <si>
+    <t>0.7934,0.0712,0.1347,0.0577</t>
+  </si>
+  <si>
+    <t>0.1760,0.6418,0.0527,0.2781</t>
+  </si>
+  <si>
+    <t>0.8480,0.0906,0.0271,0.0792</t>
+  </si>
+  <si>
+    <t>0.8216,0.0710,0.0759,0.0825</t>
+  </si>
+  <si>
+    <t>0.9851,0.0021,0.0010,0.0140</t>
+  </si>
+  <si>
+    <t>0.9897,0.0025,0.0009,0.0079</t>
+  </si>
+  <si>
+    <t>0.9736,0.0019,0.0008,0.0320</t>
+  </si>
+  <si>
+    <t>0.9811,0.0026,0.0007,0.0198</t>
+  </si>
+  <si>
+    <t>0.9911,0.0021,0.0010,0.0074</t>
+  </si>
+  <si>
+    <t>0.9926,0.0025,0.0014,0.0045</t>
+  </si>
+  <si>
+    <t>0.9842,0.0029,0.0010,0.0160</t>
+  </si>
+  <si>
+    <t>0.9887,0.0019,0.0005,0.0110</t>
+  </si>
+  <si>
+    <t>0.7730,0.3420,0.0264,0.0148</t>
+  </si>
+  <si>
+    <t>0.9550,0.0593,0.0119,0.0076</t>
+  </si>
+  <si>
+    <t>0.8038,0.2994,0.0167,0.0180</t>
+  </si>
+  <si>
+    <t>0.7899,0.0449,0.1014,0.0731</t>
+  </si>
+  <si>
+    <t>0.9767,0.0174,0.0040,0.0098</t>
+  </si>
+  <si>
+    <t>0.9595,0.0101,0.0035,0.0339</t>
+  </si>
+  <si>
+    <t>0.9803,0.0148,0.0051,0.0055</t>
+  </si>
+  <si>
+    <t>0.9845,0.0082,0.0025,0.0077</t>
+  </si>
+  <si>
+    <t>0.0083,0.0456,0.9703,0.0103</t>
+  </si>
+  <si>
+    <t>0.9710,0.0150,0.0131,0.0092</t>
+  </si>
+  <si>
+    <t>0.0144,0.0786,0.9459,0.0189</t>
+  </si>
+  <si>
+    <t>0.1000,0.3365,0.7086,0.0302</t>
+  </si>
+  <si>
+    <t>0.4052,0.0838,0.6088,0.0292</t>
+  </si>
+  <si>
+    <t>0.0224,0.5929,0.7766,0.0306</t>
+  </si>
+  <si>
+    <t>0.1113,0.0738,0.8526,0.0212</t>
+  </si>
+  <si>
+    <t>0.0210,0.0345,0.9577,0.0086</t>
+  </si>
+  <si>
+    <t>0.0129,0.0396,0.9562,0.0164</t>
+  </si>
+  <si>
+    <t>0.5451,0.1373,0.4036,0.0491</t>
+  </si>
+  <si>
+    <t>0.5934,0.1377,0.3683,0.0749</t>
+  </si>
+  <si>
+    <t>0.4642,0.0622,0.5506,0.0504</t>
+  </si>
+  <si>
+    <t>0.2161,0.5328,0.2821,0.0305</t>
+  </si>
+  <si>
+    <t>0.4251,0.1114,0.4935,0.0162</t>
+  </si>
+  <si>
+    <t>0.4491,0.4416,0.2118,0.0978</t>
+  </si>
+  <si>
+    <t>0.5840,0.2570,0.2602,0.0942</t>
+  </si>
+  <si>
+    <t>0.4309,0.2956,0.3508,0.0829</t>
+  </si>
+  <si>
+    <t>0.9650,0.0315,0.0128,0.0073</t>
+  </si>
+  <si>
+    <t>0.9591,0.0403,0.0105,0.0074</t>
+  </si>
+  <si>
+    <t>0.9676,0.0413,0.0066,0.0039</t>
+  </si>
+  <si>
+    <t>0.9893,0.0097,0.0022,0.0035</t>
+  </si>
+  <si>
+    <t>0.9686,0.0314,0.0114,0.0080</t>
+  </si>
+  <si>
+    <t>0.5061,0.2663,0.2765,0.1172</t>
+  </si>
+  <si>
+    <t>0.7324,0.0479,0.1541,0.1258</t>
+  </si>
+  <si>
+    <t>0.1700,0.1319,0.0602,0.8070</t>
+  </si>
+  <si>
+    <t>0.6609,0.1250,0.2949,0.0559</t>
+  </si>
+  <si>
+    <t>0.5293,0.0364,0.1934,0.2697</t>
+  </si>
+  <si>
+    <t>0.1124,0.0535,0.8068,0.0825</t>
+  </si>
+  <si>
+    <t>0.0787,0.5461,0.5983,0.0213</t>
+  </si>
+  <si>
+    <t>0.0997,0.3966,0.6838,0.0976</t>
+  </si>
+  <si>
+    <t>0.0259,0.4291,0.8117,0.0044</t>
+  </si>
+  <si>
+    <t>0.0150,0.1115,0.9415,0.0130</t>
+  </si>
+  <si>
+    <t>0.9921,0.0033,0.0006,0.0050</t>
+  </si>
+  <si>
+    <t>0.9955,0.0020,0.0008,0.0024</t>
+  </si>
+  <si>
+    <t>0.9944,0.0021,0.0007,0.0037</t>
+  </si>
+  <si>
+    <t>0.9915,0.0063,0.0018,0.0036</t>
+  </si>
+  <si>
+    <t>0.9911,0.0050,0.0017,0.0049</t>
+  </si>
+  <si>
+    <t>0.9942,0.0028,0.0005,0.0034</t>
+  </si>
+  <si>
+    <t>0.9949,0.0038,0.0007,0.0023</t>
+  </si>
+  <si>
+    <t>0.9941,0.0026,0.0010,0.0031</t>
+  </si>
+  <si>
+    <t>0.1915,0.0325,0.8165,0.0313</t>
+  </si>
+  <si>
+    <t>0.6128,0.1573,0.2652,0.0137</t>
+  </si>
+  <si>
+    <t>0.9319,0.0146,0.0221,0.0484</t>
+  </si>
+  <si>
+    <t>0.0044,0.0093,0.9892,0.0022</t>
+  </si>
+  <si>
+    <t>0.0102,0.0270,0.9699,0.0077</t>
+  </si>
+  <si>
+    <t>0.0745,0.2222,0.8136,0.0223</t>
+  </si>
+  <si>
+    <t>0.0112,0.0097,0.9822,0.0028</t>
+  </si>
+  <si>
+    <t>0.1420,0.0579,0.8256,0.0109</t>
+  </si>
+  <si>
+    <t>0.0013,0.0099,0.9916,0.0041</t>
+  </si>
+  <si>
+    <t>0.0603,0.4957,0.6647,0.0839</t>
+  </si>
+  <si>
+    <t>0.5100,0.1163,0.3712,0.1352</t>
+  </si>
+  <si>
+    <t>0.6204,0.0307,0.5134,0.0243</t>
+  </si>
+  <si>
+    <t>0.5679,0.0325,0.5551,0.0389</t>
+  </si>
+  <si>
+    <t>0.6930,0.0885,0.0915,0.2056</t>
+  </si>
+  <si>
+    <t>0.9899,0.0024,0.0005,0.0085</t>
+  </si>
+  <si>
+    <t>0.9920,0.0026,0.0007,0.0059</t>
+  </si>
+  <si>
+    <t>0.9917,0.0018,0.0005,0.0077</t>
+  </si>
+  <si>
+    <t>0.9868,0.0092,0.0029,0.0056</t>
+  </si>
+  <si>
+    <t>0.9793,0.0018,0.0005,0.0259</t>
+  </si>
+  <si>
+    <t>0.9955,0.0033,0.0006,0.0021</t>
+  </si>
+  <si>
+    <t>0.9940,0.0025,0.0007,0.0038</t>
+  </si>
+  <si>
+    <t>0.9969,0.0019,0.0004,0.0016</t>
+  </si>
+  <si>
+    <t>0.0808,0.5060,0.5891,0.0269</t>
+  </si>
+  <si>
+    <t>0.0164,0.0272,0.9646,0.0080</t>
+  </si>
+  <si>
+    <t>0.0188,0.4730,0.8283,0.0083</t>
+  </si>
+  <si>
+    <t>0.3551,0.1015,0.6018,0.0416</t>
+  </si>
+  <si>
+    <t>0.0194,0.0089,0.9690,0.0069</t>
+  </si>
+  <si>
+    <t>0.1032,0.0572,0.2949,0.7303</t>
+  </si>
+  <si>
+    <t>0.1953,0.1566,0.4561,0.4496</t>
+  </si>
+  <si>
+    <t>0.1426,0.1205,0.7821,0.0389</t>
+  </si>
+  <si>
+    <t>0.6465,0.0032,0.0036,0.4886</t>
+  </si>
+  <si>
+    <t>0.0164,0.0288,0.0029,0.9811</t>
+  </si>
+  <si>
+    <t>0.1588,0.0051,0.0020,0.9201</t>
+  </si>
+  <si>
+    <t>0.0025,0.0007,0.0004,0.9982</t>
+  </si>
+  <si>
+    <t>0.0035,0.0005,0.0001,0.9983</t>
+  </si>
+  <si>
+    <t>0.5002,0.0786,0.0098,0.4301</t>
   </si>
 </sst>
 </file>
@@ -1953,7 +1953,7 @@
         <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D2" t="s">
         <v>264</v>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1981,7 +1981,7 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
         <v>266</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2233,7 +2233,7 @@
         <v>262</v>
       </c>
       <c r="C22" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D22" t="s">
         <v>284</v>
@@ -2247,7 +2247,7 @@
         <v>262</v>
       </c>
       <c r="C23" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D23" t="s">
         <v>285</v>
@@ -2275,7 +2275,7 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
         <v>287</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2345,7 +2345,7 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
         <v>292</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2569,7 +2569,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>308</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2625,7 +2625,7 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D50" t="s">
         <v>312</v>
@@ -2639,7 +2639,7 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
         <v>313</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2821,7 +2821,7 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
         <v>326</v>
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3101,7 +3101,7 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
         <v>346</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3465,7 +3465,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
         <v>372</v>
@@ -3493,7 +3493,7 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D112" t="s">
         <v>374</v>
@@ -3507,7 +3507,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4081,7 +4081,7 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
         <v>416</v>
@@ -4193,7 +4193,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
         <v>424</v>
@@ -4347,7 +4347,7 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
         <v>435</v>
@@ -4459,7 +4459,7 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D181" t="s">
         <v>443</v>
@@ -4487,7 +4487,7 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
         <v>445</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4529,7 +4529,7 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D186" t="s">
         <v>448</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4557,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
         <v>450</v>
@@ -4571,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
         <v>451</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4613,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
         <v>454</v>
@@ -4627,7 +4627,7 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D193" t="s">
         <v>455</v>
@@ -4795,7 +4795,7 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D205" t="s">
         <v>467</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5075,7 +5075,7 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D225" t="s">
         <v>487</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5173,7 +5173,7 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
         <v>494</v>
@@ -5187,7 +5187,7 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D233" t="s">
         <v>495</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5355,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
         <v>507</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
